--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/3. 变更水价.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/3. 变更水价.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="340">
   <si>
     <t>业务属性</t>
   </si>
@@ -316,9 +316,6 @@
     <t>自由文本，非空</t>
   </si>
   <si>
-    <t>NVARCHAR2</t>
-  </si>
-  <si>
     <t>支持中文、自由文本</t>
   </si>
   <si>
@@ -457,7 +454,7 @@
     <t>关联水表口径字典</t>
   </si>
   <si>
-    <t>mm</t>
+    <t>毫米</t>
   </si>
   <si>
     <t>关联口径字典</t>
@@ -523,7 +520,7 @@
     <t>表卡前3个月的月均用水量</t>
   </si>
   <si>
-    <t>吨</t>
+    <t>立方米</t>
   </si>
   <si>
     <t>仅允许数值</t>
@@ -562,7 +559,7 @@
     <t>关联水价信息字典(PRICE_INFO)</t>
   </si>
   <si>
-    <t>元/吨</t>
+    <t>元/立方米</t>
   </si>
   <si>
     <t>关联用水性质字典</t>
@@ -1049,7 +1046,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,13 +1108,6 @@
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1678,48 +1668,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1729,97 +1722,94 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2754,13 +2744,13 @@
         <v>77</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>79</v>
       </c>
       <c r="R6" s="4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S6" s="4" t="s">
         <v>75</v>
@@ -2784,7 +2774,7 @@
         <v>83</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA6" s="5" t="s">
         <v>85</v>
@@ -2793,21 +2783,21 @@
         <v>86</v>
       </c>
       <c r="AC6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD6" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD6" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:30">
       <c r="A7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>69</v>
@@ -2822,10 +2812,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>75</v>
@@ -2846,13 +2836,13 @@
         <v>77</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R7" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>75</v>
@@ -2876,7 +2866,7 @@
         <v>83</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>85</v>
@@ -2885,21 +2875,21 @@
         <v>86</v>
       </c>
       <c r="AC7" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD7" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD7" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:30">
       <c r="A8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>69</v>
@@ -2914,10 +2904,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>75</v>
@@ -2968,10 +2958,10 @@
         <v>83</v>
       </c>
       <c r="Z8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA8" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="AA8" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="AB8" s="4" t="s">
         <v>86</v>
@@ -2985,13 +2975,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:30">
       <c r="A9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>69</v>
@@ -3006,10 +2996,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>120</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>75</v>
@@ -3060,10 +3050,10 @@
         <v>83</v>
       </c>
       <c r="Z9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA9" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="AB9" s="6" t="s">
         <v>86</v>
@@ -3077,13 +3067,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:30">
       <c r="A10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>69</v>
@@ -3098,10 +3088,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>75</v>
@@ -3122,10 +3112,10 @@
         <v>77</v>
       </c>
       <c r="P10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q10" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R10" s="4">
         <v>22</v>
@@ -3152,10 +3142,10 @@
         <v>83</v>
       </c>
       <c r="Z10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA10" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="AB10" s="4" t="s">
         <v>86</v>
@@ -3169,13 +3159,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:30">
       <c r="A11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>69</v>
@@ -3190,10 +3180,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>75</v>
@@ -3261,13 +3251,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:30">
       <c r="A12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>69</v>
@@ -3282,10 +3272,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>75</v>
@@ -3353,13 +3343,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:30">
       <c r="A13" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>69</v>
@@ -3374,10 +3364,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>75</v>
@@ -3398,10 +3388,10 @@
         <v>77</v>
       </c>
       <c r="P13" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R13" s="6">
         <v>22</v>
@@ -3410,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>80</v>
@@ -3428,10 +3418,10 @@
         <v>83</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AB13" s="6" t="s">
         <v>86</v>
@@ -3445,13 +3435,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:30">
       <c r="A14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>69</v>
@@ -3466,10 +3456,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>75</v>
@@ -3490,10 +3480,10 @@
         <v>77</v>
       </c>
       <c r="P14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q14" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R14" s="4">
         <v>22</v>
@@ -3501,8 +3491,8 @@
       <c r="S14" s="4">
         <v>0</v>
       </c>
-      <c r="T14" s="4" t="s">
-        <v>147</v>
+      <c r="T14" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="U14" s="4" t="s">
         <v>80</v>
@@ -3520,10 +3510,10 @@
         <v>83</v>
       </c>
       <c r="Z14" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA14" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AB14" s="4" t="s">
         <v>86</v>
@@ -3537,13 +3527,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:30">
       <c r="A15" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>69</v>
@@ -3558,7 +3548,7 @@
         <v>72</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>85</v>
@@ -3582,13 +3572,13 @@
         <v>77</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R15" s="6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>75</v>
@@ -3612,7 +3602,7 @@
         <v>83</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>85</v>
@@ -3629,13 +3619,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:30">
       <c r="A16" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
@@ -3650,10 +3640,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>75</v>
@@ -3674,7 +3664,7 @@
         <v>77</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q16" s="4" t="s">
         <v>79</v>
@@ -3704,10 +3694,10 @@
         <v>83</v>
       </c>
       <c r="Z16" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA16" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AB16" s="4" t="s">
         <v>86</v>
@@ -3721,13 +3711,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:30">
       <c r="A17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>69</v>
@@ -3742,10 +3732,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>75</v>
@@ -3766,10 +3756,10 @@
         <v>77</v>
       </c>
       <c r="P17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R17" s="6">
         <v>22</v>
@@ -3777,8 +3767,8 @@
       <c r="S17" s="6">
         <v>0</v>
       </c>
-      <c r="T17" s="6" t="s">
-        <v>169</v>
+      <c r="T17" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="U17" s="6" t="s">
         <v>80</v>
@@ -3796,10 +3786,10 @@
         <v>83</v>
       </c>
       <c r="Z17" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA17" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="AA17" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="AB17" s="6" t="s">
         <v>86</v>
@@ -3813,13 +3803,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:30">
       <c r="A18" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>69</v>
@@ -3834,10 +3824,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>75</v>
@@ -3858,10 +3848,10 @@
         <v>77</v>
       </c>
       <c r="P18" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q18" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R18" s="4">
         <v>22</v>
@@ -3888,10 +3878,10 @@
         <v>83</v>
       </c>
       <c r="Z18" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA18" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AB18" s="4" t="s">
         <v>86</v>
@@ -3905,13 +3895,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:30">
       <c r="A19" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>69</v>
@@ -3926,10 +3916,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>75</v>
@@ -3961,8 +3951,8 @@
       <c r="S19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="T19" s="6" t="s">
-        <v>182</v>
+      <c r="T19" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="U19" s="6" t="s">
         <v>80</v>
@@ -3980,10 +3970,10 @@
         <v>83</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA19" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AB19" s="6" t="s">
         <v>86</v>
@@ -3997,13 +3987,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:30">
       <c r="A20" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>69</v>
@@ -4018,10 +4008,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>75</v>
@@ -4054,7 +4044,7 @@
         <v>75</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U20" s="4" t="s">
         <v>80</v>
@@ -4072,10 +4062,10 @@
         <v>83</v>
       </c>
       <c r="Z20" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA20" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AB20" s="4" t="s">
         <v>86</v>
@@ -4089,13 +4079,13 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:30">
       <c r="A21" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>69</v>
@@ -4110,10 +4100,10 @@
         <v>72</v>
       </c>
       <c r="H21" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>75</v>
@@ -4134,10 +4124,10 @@
         <v>77</v>
       </c>
       <c r="P21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q21" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q21" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R21" s="6">
         <v>22</v>
@@ -4145,8 +4135,8 @@
       <c r="S21" s="6">
         <v>4</v>
       </c>
-      <c r="T21" s="6" t="s">
-        <v>182</v>
+      <c r="T21" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="U21" s="6" t="s">
         <v>80</v>
@@ -4164,10 +4154,10 @@
         <v>83</v>
       </c>
       <c r="Z21" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA21" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="AA21" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="AB21" s="6" t="s">
         <v>86</v>
@@ -4181,13 +4171,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:30">
       <c r="A22" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>69</v>
@@ -4202,10 +4192,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>75</v>
@@ -4226,10 +4216,10 @@
         <v>77</v>
       </c>
       <c r="P22" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q22" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R22" s="4">
         <v>22</v>
@@ -4238,7 +4228,7 @@
         <v>4</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U22" s="4" t="s">
         <v>80</v>
@@ -4256,10 +4246,10 @@
         <v>83</v>
       </c>
       <c r="Z22" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA22" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="AA22" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="AB22" s="4" t="s">
         <v>86</v>
@@ -4273,13 +4263,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:30">
       <c r="A23" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>69</v>
@@ -4294,10 +4284,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>200</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>201</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>75</v>
@@ -4318,10 +4308,10 @@
         <v>77</v>
       </c>
       <c r="P23" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q23" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q23" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R23" s="6">
         <v>22</v>
@@ -4348,10 +4338,10 @@
         <v>83</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA23" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AB23" s="6" t="s">
         <v>86</v>
@@ -4365,13 +4355,13 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:30">
       <c r="A24" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>69</v>
@@ -4386,10 +4376,10 @@
         <v>72</v>
       </c>
       <c r="H24" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>75</v>
@@ -4410,7 +4400,7 @@
         <v>77</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q24" s="4" t="s">
         <v>79</v>
@@ -4440,10 +4430,10 @@
         <v>83</v>
       </c>
       <c r="Z24" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA24" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="AA24" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="AB24" s="4" t="s">
         <v>86</v>
@@ -4457,13 +4447,13 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:30">
       <c r="A25" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>69</v>
@@ -4478,7 +4468,7 @@
         <v>72</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>99</v>
@@ -4502,13 +4492,13 @@
         <v>77</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R25" s="6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>75</v>
@@ -4532,7 +4522,7 @@
         <v>83</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA25" s="7" t="s">
         <v>85</v>
@@ -4541,21 +4531,21 @@
         <v>86</v>
       </c>
       <c r="AC25" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD25" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD25" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:30">
       <c r="A26" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>69</v>
@@ -4570,10 +4560,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>75</v>
@@ -4594,10 +4584,10 @@
         <v>77</v>
       </c>
       <c r="P26" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q26" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R26" s="4">
         <v>22</v>
@@ -4624,10 +4614,10 @@
         <v>83</v>
       </c>
       <c r="Z26" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA26" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AB26" s="4" t="s">
         <v>86</v>
@@ -4641,13 +4631,13 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:30">
       <c r="A27" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>69</v>
@@ -4662,10 +4652,10 @@
         <v>72</v>
       </c>
       <c r="H27" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>224</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>225</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>75</v>
@@ -4686,10 +4676,10 @@
         <v>77</v>
       </c>
       <c r="P27" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q27" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="Q27" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="R27" s="6">
         <v>7</v>
@@ -4716,10 +4706,10 @@
         <v>83</v>
       </c>
       <c r="Z27" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA27" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="AB27" s="6" t="s">
         <v>86</v>
@@ -4733,13 +4723,13 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:30">
       <c r="A28" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>69</v>
@@ -4754,10 +4744,10 @@
         <v>72</v>
       </c>
       <c r="H28" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>75</v>
@@ -4808,30 +4798,30 @@
         <v>83</v>
       </c>
       <c r="Z28" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AA28" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB28" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC28" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="AC28" s="29" t="s">
+      <c r="AD28" s="30" t="s">
         <v>237</v>
-      </c>
-      <c r="AD28" s="30" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:30">
       <c r="A29" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>69</v>
@@ -4846,10 +4836,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>242</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>243</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>75</v>
@@ -4900,30 +4890,30 @@
         <v>83</v>
       </c>
       <c r="Z29" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB29" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC29" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="AC29" s="31" t="s">
+      <c r="AD29" s="30" t="s">
         <v>237</v>
-      </c>
-      <c r="AD29" s="30" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:30">
       <c r="A30" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>69</v>
@@ -4938,10 +4928,10 @@
         <v>72</v>
       </c>
       <c r="H30" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>75</v>
@@ -4962,10 +4952,10 @@
         <v>77</v>
       </c>
       <c r="P30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q30" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R30" s="4">
         <v>22</v>
@@ -4992,10 +4982,10 @@
         <v>83</v>
       </c>
       <c r="Z30" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA30" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="AA30" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="AB30" s="4" t="s">
         <v>86</v>
@@ -5009,13 +4999,13 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:30">
       <c r="A31" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>69</v>
@@ -5030,10 +5020,10 @@
         <v>72</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>75</v>
@@ -5054,10 +5044,10 @@
         <v>77</v>
       </c>
       <c r="P31" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q31" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="Q31" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="R31" s="6">
         <v>7</v>
@@ -5084,10 +5074,10 @@
         <v>83</v>
       </c>
       <c r="Z31" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA31" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="AA31" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="AB31" s="6" t="s">
         <v>86</v>
@@ -5101,13 +5091,13 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:30">
       <c r="A32" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>69</v>
@@ -5122,10 +5112,10 @@
         <v>72</v>
       </c>
       <c r="H32" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>75</v>
@@ -5146,10 +5136,10 @@
         <v>77</v>
       </c>
       <c r="P32" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q32" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q32" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R32" s="4">
         <v>22</v>
@@ -5176,10 +5166,10 @@
         <v>83</v>
       </c>
       <c r="Z32" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA32" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="AA32" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="AB32" s="4" t="s">
         <v>86</v>
@@ -5193,13 +5183,13 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:30">
       <c r="A33" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>69</v>
@@ -5214,10 +5204,10 @@
         <v>72</v>
       </c>
       <c r="H33" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>262</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>263</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>75</v>
@@ -5238,10 +5228,10 @@
         <v>77</v>
       </c>
       <c r="P33" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q33" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="Q33" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="R33" s="6">
         <v>7</v>
@@ -5268,10 +5258,10 @@
         <v>83</v>
       </c>
       <c r="Z33" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA33" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="AA33" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="AB33" s="6" t="s">
         <v>86</v>
@@ -5285,13 +5275,13 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:30">
       <c r="A34" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>69</v>
@@ -5306,10 +5296,10 @@
         <v>72</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>75</v>
@@ -5330,10 +5320,10 @@
         <v>77</v>
       </c>
       <c r="P34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q34" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q34" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R34" s="4">
         <v>22</v>
@@ -5360,10 +5350,10 @@
         <v>83</v>
       </c>
       <c r="Z34" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA34" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="AA34" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="AB34" s="4" t="s">
         <v>86</v>
@@ -5377,13 +5367,13 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:30">
       <c r="A35" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>69</v>
@@ -5398,10 +5388,10 @@
         <v>72</v>
       </c>
       <c r="H35" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>75</v>
@@ -5422,10 +5412,10 @@
         <v>77</v>
       </c>
       <c r="P35" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q35" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="Q35" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="R35" s="6">
         <v>7</v>
@@ -5452,10 +5442,10 @@
         <v>83</v>
       </c>
       <c r="Z35" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA35" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="AA35" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="AB35" s="6" t="s">
         <v>86</v>
@@ -5469,13 +5459,13 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:30">
       <c r="A36" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>275</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>69</v>
@@ -5490,10 +5480,10 @@
         <v>72</v>
       </c>
       <c r="H36" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>75</v>
@@ -5547,10 +5537,10 @@
         <v>85</v>
       </c>
       <c r="AA36" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AB36" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC36" s="23" t="s">
         <v>87</v>
@@ -5561,13 +5551,13 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:30">
       <c r="A37" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>69</v>
@@ -5582,10 +5572,10 @@
         <v>72</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>283</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>75</v>
@@ -5639,27 +5629,27 @@
         <v>84</v>
       </c>
       <c r="AA37" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AB37" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC37" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD37" s="27" t="s">
         <v>102</v>
-      </c>
-      <c r="AD37" s="27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:30">
       <c r="A38" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>69</v>
@@ -5674,10 +5664,10 @@
         <v>72</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>75</v>
@@ -5698,7 +5688,7 @@
         <v>77</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q38" s="4" t="s">
         <v>79</v>
@@ -5728,13 +5718,13 @@
         <v>83</v>
       </c>
       <c r="Z38" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA38" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC38" s="23" t="s">
         <v>87</v>
@@ -5745,13 +5735,13 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:30">
       <c r="A39" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>291</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>69</v>
@@ -5766,10 +5756,10 @@
         <v>72</v>
       </c>
       <c r="H39" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>292</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>293</v>
       </c>
       <c r="J39" s="7" t="s">
         <v>75</v>
@@ -5790,10 +5780,10 @@
         <v>77</v>
       </c>
       <c r="P39" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q39" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q39" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R39" s="6">
         <v>22</v>
@@ -5820,13 +5810,13 @@
         <v>83</v>
       </c>
       <c r="Z39" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA39" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB39" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC39" s="25" t="s">
         <v>87</v>
@@ -5837,13 +5827,13 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:30">
       <c r="A40" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>69</v>
@@ -5858,10 +5848,10 @@
         <v>72</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>75</v>
@@ -5882,7 +5872,7 @@
         <v>77</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="Q40" s="4" t="s">
         <v>79</v>
@@ -5912,13 +5902,13 @@
         <v>83</v>
       </c>
       <c r="Z40" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA40" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB40" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC40" s="23" t="s">
         <v>87</v>
@@ -5929,13 +5919,13 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:30">
       <c r="A41" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>300</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>69</v>
@@ -5950,10 +5940,10 @@
         <v>72</v>
       </c>
       <c r="H41" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>302</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>303</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>75</v>
@@ -5974,10 +5964,10 @@
         <v>77</v>
       </c>
       <c r="P41" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q41" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R41" s="6">
         <v>22</v>
@@ -5985,8 +5975,8 @@
       <c r="S41" s="6">
         <v>4</v>
       </c>
-      <c r="T41" s="6" t="s">
-        <v>182</v>
+      <c r="T41" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>80</v>
@@ -6004,13 +5994,13 @@
         <v>83</v>
       </c>
       <c r="Z41" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA41" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="AA41" s="7" t="s">
-        <v>171</v>
-      </c>
       <c r="AB41" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC41" s="25" t="s">
         <v>87</v>
@@ -6021,13 +6011,13 @@
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:30">
       <c r="A42" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>69</v>
@@ -6042,10 +6032,10 @@
         <v>72</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>75</v>
@@ -6066,10 +6056,10 @@
         <v>77</v>
       </c>
       <c r="P42" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q42" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q42" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R42" s="4">
         <v>22</v>
@@ -6078,7 +6068,7 @@
         <v>4</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U42" s="4" t="s">
         <v>80</v>
@@ -6096,13 +6086,13 @@
         <v>83</v>
       </c>
       <c r="Z42" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA42" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AA42" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="AB42" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC42" s="23" t="s">
         <v>87</v>
@@ -6113,13 +6103,13 @@
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:30">
       <c r="A43" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>69</v>
@@ -6134,10 +6124,10 @@
         <v>72</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>75</v>
@@ -6188,30 +6178,30 @@
         <v>83</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AA43" s="7" t="s">
         <v>85</v>
       </c>
       <c r="AB43" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC43" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="AC43" s="31" t="s">
+      <c r="AD43" s="30" t="s">
         <v>237</v>
-      </c>
-      <c r="AD43" s="30" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:30">
       <c r="A44" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>69</v>
@@ -6226,10 +6216,10 @@
         <v>72</v>
       </c>
       <c r="H44" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>317</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>75</v>
@@ -6250,10 +6240,10 @@
         <v>77</v>
       </c>
       <c r="P44" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q44" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q44" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R44" s="4">
         <v>22</v>
@@ -6262,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U44" s="4" t="s">
         <v>80</v>
@@ -6280,10 +6270,10 @@
         <v>83</v>
       </c>
       <c r="Z44" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA44" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB44" s="4" t="s">
         <v>86</v>
@@ -6297,13 +6287,13 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:30">
       <c r="A45" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>320</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>69</v>
@@ -6318,10 +6308,10 @@
         <v>72</v>
       </c>
       <c r="H45" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>322</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>75</v>
@@ -6342,10 +6332,10 @@
         <v>77</v>
       </c>
       <c r="P45" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q45" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q45" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R45" s="6">
         <v>22</v>
@@ -6353,8 +6343,8 @@
       <c r="S45" s="6">
         <v>0</v>
       </c>
-      <c r="T45" s="6" t="s">
-        <v>169</v>
+      <c r="T45" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>80</v>
@@ -6372,10 +6362,10 @@
         <v>83</v>
       </c>
       <c r="Z45" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA45" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="AA45" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="AB45" s="6" t="s">
         <v>86</v>
@@ -6389,13 +6379,13 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:30">
       <c r="A46" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>325</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>69</v>
@@ -6410,10 +6400,10 @@
         <v>72</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>75</v>
@@ -6434,10 +6424,10 @@
         <v>77</v>
       </c>
       <c r="P46" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q46" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="Q46" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="R46" s="4">
         <v>22</v>
@@ -6446,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U46" s="4" t="s">
         <v>80</v>
@@ -6464,10 +6454,10 @@
         <v>83</v>
       </c>
       <c r="Z46" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA46" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="AA46" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="AB46" s="4" t="s">
         <v>86</v>
@@ -6481,13 +6471,13 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:30">
       <c r="A47" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>69</v>
@@ -6502,10 +6492,10 @@
         <v>72</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>75</v>
@@ -6526,10 +6516,10 @@
         <v>77</v>
       </c>
       <c r="P47" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q47" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="Q47" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="R47" s="6">
         <v>22</v>
@@ -6537,8 +6527,8 @@
       <c r="S47" s="6">
         <v>0</v>
       </c>
-      <c r="T47" s="6" t="s">
-        <v>169</v>
+      <c r="T47" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="U47" s="6" t="s">
         <v>80</v>
@@ -6556,10 +6546,10 @@
         <v>83</v>
       </c>
       <c r="Z47" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA47" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="AA47" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="AB47" s="6" t="s">
         <v>86</v>
@@ -6573,13 +6563,13 @@
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:30">
       <c r="A48" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>333</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>69</v>
@@ -6594,10 +6584,10 @@
         <v>72</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>75</v>
@@ -6630,7 +6620,7 @@
         <v>75</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U48" s="4" t="s">
         <v>80</v>
@@ -6648,13 +6638,13 @@
         <v>83</v>
       </c>
       <c r="Z48" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AA48" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC48" s="23" t="s">
         <v>87</v>
@@ -6665,13 +6655,13 @@
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:30">
       <c r="A49" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>69</v>
@@ -6686,10 +6676,10 @@
         <v>72</v>
       </c>
       <c r="H49" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>339</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>75</v>
@@ -6740,13 +6730,13 @@
         <v>83</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AA49" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB49" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AC49" s="25" t="s">
         <v>87</v>
